--- a/outputs/evaluation/requirement/design/v2/gemini-3-1-flash-lite/CF_M08/third/CF_M08_req_eval.xlsx
+++ b/outputs/evaluation/requirement/design/v2/gemini-3-1-flash-lite/CF_M08/third/CF_M08_req_eval.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -546,6 +551,9 @@
         <v>0.7742</v>
       </c>
       <c r="D13" t="n">
+        <v>0.8571</v>
+      </c>
+      <c r="E13" t="n">
         <v>0.9359</v>
       </c>
     </row>
@@ -760,9 +768,6 @@
           <t>C_01</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>QR</t>
@@ -786,8 +791,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -818,10 +821,6 @@
           <t>The system shall provide an affiliation/plan system for companies (free, basic, premium).</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>Constraint</t>
@@ -835,10 +834,6 @@
           <t>The system should have three different membership plans: free, basic and premium.</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -869,14 +864,11 @@
           <t>Users shall be able to create an account as either a company or a donor.</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>FR</t>
@@ -890,10 +882,6 @@
           <t>A user can be both a donor and a company.</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -924,10 +912,6 @@
           <t>The system shall allow logged-in users to view company profiles and their products.</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>FR</t>
@@ -941,10 +925,6 @@
           <t>The system must allow users logged-in or non-logged-in to see the profiles and products of the different companies.</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -975,14 +955,11 @@
           <t>Compatibility tests must demonstrate functionality across major browsers and mobile devices.</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>R_22</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -996,14 +973,11 @@
           <t>Evidence of compatibility that they demonstrate functionality in the main browsers (Chrome, Firefox, Safari, Edge) and mobile devices.</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>CF_M08_R25</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1034,10 +1008,6 @@
           <t>A company shall have access to a dashboard for internal functionalities and information.</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1051,10 +1021,6 @@
           <t>A company must have access to the system dashboard to be able to use the different ones internal functionalities and additional information (statistics, values, etc.).</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1085,14 +1051,11 @@
           <t>Uptime monitoring must demonstrate 99.9% availability and disaster recovery tests must meet the 1-hour recovery time.</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>R_20</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1106,14 +1069,11 @@
           <t>Uptime monitoring demonstrating 99.9% uptime and disaster recovery testing that meets the specified recovery time.</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>CF_M08_R21</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1144,14 +1104,11 @@
           <t>Verify that only the company user can access their specific products, routes, and profile.</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>R_24</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1165,14 +1122,11 @@
           <t>Verify that only Business Users can access their products/routes/profile.</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>CF_M08_R29</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1203,14 +1157,11 @@
           <t>The system interface shall be available in Spanish and English, verified by a translator.</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>R_14</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1224,14 +1175,11 @@
           <t>The system should support Spanish and English (verified by a translator).</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>CF_M08_R15</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1262,10 +1210,6 @@
           <t>A company shall be able to modify its public profile and preview it while editing.</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1279,10 +1223,6 @@
           <t>A company must be able to modify its public profile/page at any time and preview it while editing</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1313,10 +1253,6 @@
           <t>The system shall store all images of products and users.</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1330,10 +1266,6 @@
           <t>The system must be able to save all the images of all the products and users of the system.</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1364,10 +1296,6 @@
           <t>A company shall be able to register a route to link it to its products.</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1381,10 +1309,6 @@
           <t>A company must be able to register a route to link it to its products.</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1415,10 +1339,6 @@
           <t>The system shall authenticate existing users via email.</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1432,10 +1352,6 @@
           <t>The system must be able to authenticate existing users through email.</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1471,9 +1387,6 @@
           <t>C_03</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1497,8 +1410,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1529,10 +1440,6 @@
           <t>A company shall be able to register a product to be visible on its public profile.</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1546,10 +1453,6 @@
           <t>A company must be able to register a product and have it visible on its profile/page public.</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1580,10 +1483,6 @@
           <t>The system shall allow registering new users.</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1597,10 +1496,6 @@
           <t>The system must allow new users to register in the system.</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1631,14 +1526,11 @@
           <t>Usability testing with at least 10 representative users shall achieve a minimum satisfaction score of 8/10.</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>R_16</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1652,14 +1544,11 @@
           <t>Performance of usability tests with at least 10 representative users, achieving a minimum satisfaction score of 8/10.</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>CF_M08_R17</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1690,10 +1579,6 @@
           <t>The system shall allow users to log out.</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1707,10 +1592,6 @@
           <t>The system must allow users to log out.</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1746,9 +1627,6 @@
           <t>C_04</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1767,9 +1645,6 @@
           <t>CF_M08_C04</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1800,10 +1675,6 @@
           <t>Products, routes, and company profiles can only be edited and accessed by the owning company.</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1827,8 +1698,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1859,10 +1728,6 @@
           <t>A user shall be able to return a product registered by a company using its routes.</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1876,10 +1741,6 @@
           <t>A user must be able to return a product registered in a company throug the use of its routes.</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1910,14 +1771,11 @@
           <t>The system must pass security audits without critical vulnerabilities.</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>R_18</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1931,14 +1789,11 @@
           <t xml:space="preserve"> The system must pass security audits data without critical vulnerabilities.</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>CF_M08_R19</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1974,9 +1829,6 @@
           <t>C_05</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>QR</t>
@@ -2000,8 +1852,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2037,9 +1887,6 @@
           <t>C_02</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>QR</t>
@@ -2063,8 +1910,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
